--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9393,0.0227,0.0205,0.0037</t>
-  </si>
-  <si>
-    <t>0.8551,0.0633,0.0577,0.0119</t>
-  </si>
-  <si>
-    <t>0.9666,0.0113,0.0087,0.0034</t>
-  </si>
-  <si>
-    <t>0.9435,0.0229,0.0085,0.0035</t>
-  </si>
-  <si>
-    <t>0.7793,0.2028,0.0133,0.0069</t>
-  </si>
-  <si>
-    <t>0.8623,0.0669,0.0079,0.0075</t>
-  </si>
-  <si>
-    <t>0.8461,0.1404,0.0107,0.0042</t>
-  </si>
-  <si>
-    <t>0.9167,0.0486,0.0029,0.0017</t>
-  </si>
-  <si>
-    <t>0.6738,0.2888,0.0424,0.0166</t>
-  </si>
-  <si>
-    <t>0.7526,0.1470,0.0271,0.0264</t>
-  </si>
-  <si>
-    <t>0.6146,0.1004,0.0380,0.1649</t>
-  </si>
-  <si>
-    <t>0.9171,0.0286,0.0024,0.0048</t>
-  </si>
-  <si>
-    <t>0.9844,0.0043,0.0073,0.0002</t>
-  </si>
-  <si>
-    <t>0.9719,0.0146,0.0080,0.0003</t>
-  </si>
-  <si>
-    <t>0.9437,0.0219,0.0306,0.0013</t>
-  </si>
-  <si>
-    <t>0.8295,0.0859,0.0730,0.0032</t>
-  </si>
-  <si>
-    <t>0.9313,0.0248,0.0296,0.0018</t>
-  </si>
-  <si>
-    <t>0.8628,0.1863,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.4059,0.6283,0.0155,0.0012</t>
-  </si>
-  <si>
-    <t>0.6986,0.3845,0.0077,0.0012</t>
-  </si>
-  <si>
-    <t>0.5856,0.5057,0.0091,0.0012</t>
-  </si>
-  <si>
-    <t>0.2100,0.8587,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.9287,0.0357,0.0255,0.0029</t>
-  </si>
-  <si>
-    <t>0.9920,0.0009,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.9709,0.0020,0.0613,0.0004</t>
-  </si>
-  <si>
-    <t>0.9715,0.0075,0.0128,0.0003</t>
-  </si>
-  <si>
-    <t>0.9105,0.0168,0.1038,0.0018</t>
-  </si>
-  <si>
-    <t>0.9774,0.0034,0.0158,0.0013</t>
-  </si>
-  <si>
-    <t>0.9542,0.0037,0.0820,0.0001</t>
-  </si>
-  <si>
-    <t>0.8029,0.2258,0.0251,0.0014</t>
-  </si>
-  <si>
-    <t>0.9097,0.0791,0.0154,0.0009</t>
-  </si>
-  <si>
-    <t>0.0340,0.2005,0.9542,0.0027</t>
-  </si>
-  <si>
-    <t>0.8574,0.1921,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.9339,0.0472,0.0086,0.0028</t>
-  </si>
-  <si>
-    <t>0.9036,0.0728,0.0180,0.0036</t>
-  </si>
-  <si>
-    <t>0.5849,0.4955,0.0090,0.0024</t>
-  </si>
-  <si>
-    <t>0.8978,0.1084,0.0135,0.0012</t>
-  </si>
-  <si>
-    <t>0.4381,0.1506,0.5433,0.0061</t>
-  </si>
-  <si>
-    <t>0.8049,0.0516,0.2210,0.0020</t>
-  </si>
-  <si>
-    <t>0.8926,0.0311,0.0745,0.0033</t>
-  </si>
-  <si>
-    <t>0.9785,0.0041,0.0100,0.0019</t>
-  </si>
-  <si>
-    <t>0.8704,0.0411,0.1076,0.0009</t>
-  </si>
-  <si>
-    <t>0.7389,0.1548,0.1024,0.0009</t>
-  </si>
-  <si>
-    <t>0.9574,0.0130,0.0278,0.0006</t>
-  </si>
-  <si>
-    <t>0.9244,0.0743,0.0066,0.0006</t>
-  </si>
-  <si>
-    <t>0.8493,0.1774,0.0086,0.0008</t>
-  </si>
-  <si>
-    <t>0.7535,0.3856,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.4514,0.6820,0.0081,0.0005</t>
-  </si>
-  <si>
-    <t>0.6180,0.0844,0.4459,0.0025</t>
-  </si>
-  <si>
-    <t>0.1443,0.5019,0.6253,0.0012</t>
-  </si>
-  <si>
-    <t>0.9707,0.0042,0.0283,0.0004</t>
-  </si>
-  <si>
-    <t>0.8784,0.0520,0.0519,0.0007</t>
-  </si>
-  <si>
-    <t>0.6296,0.0336,0.4527,0.0015</t>
-  </si>
-  <si>
-    <t>0.9086,0.0201,0.0973,0.0006</t>
-  </si>
-  <si>
-    <t>0.8310,0.1249,0.0235,0.0090</t>
-  </si>
-  <si>
-    <t>0.8287,0.1391,0.0140,0.0075</t>
-  </si>
-  <si>
-    <t>0.9488,0.0240,0.0100,0.0060</t>
-  </si>
-  <si>
-    <t>0.1500,0.4503,0.7690,0.0188</t>
-  </si>
-  <si>
-    <t>0.8977,0.0571,0.0194,0.0084</t>
-  </si>
-  <si>
-    <t>0.7820,0.1838,0.0112,0.0114</t>
-  </si>
-  <si>
-    <t>0.8532,0.1073,0.0139,0.0065</t>
-  </si>
-  <si>
-    <t>0.0043,0.9500,0.9244,0.0007</t>
-  </si>
-  <si>
-    <t>0.3287,0.2662,0.5400,0.0007</t>
-  </si>
-  <si>
-    <t>0.4623,0.0468,0.6658,0.0011</t>
-  </si>
-  <si>
-    <t>0.0075,0.9109,0.9118,0.0004</t>
-  </si>
-  <si>
-    <t>0.2789,0.0579,0.8167,0.0009</t>
-  </si>
-  <si>
-    <t>0.9445,0.0505,0.0079,0.0004</t>
-  </si>
-  <si>
-    <t>0.3780,0.7813,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.9060,0.0544,0.0382,0.0015</t>
-  </si>
-  <si>
-    <t>0.8400,0.0859,0.0392,0.0055</t>
-  </si>
-  <si>
-    <t>0.0544,0.2800,0.8192,0.0031</t>
-  </si>
-  <si>
-    <t>0.6303,0.2468,0.1386,0.0025</t>
-  </si>
-  <si>
-    <t>0.2499,0.6377,0.2941,0.0073</t>
-  </si>
-  <si>
-    <t>0.0733,0.8857,0.3285,0.0003</t>
-  </si>
-  <si>
-    <t>0.3018,0.5706,0.2387,0.0020</t>
-  </si>
-  <si>
-    <t>0.9129,0.0205,0.0767,0.0031</t>
-  </si>
-  <si>
-    <t>0.7942,0.0205,0.0505,0.0716</t>
-  </si>
-  <si>
-    <t>0.9830,0.0013,0.0099,0.0018</t>
-  </si>
-  <si>
-    <t>0.9545,0.0077,0.0129,0.0101</t>
-  </si>
-  <si>
-    <t>0.9131,0.0302,0.0468,0.0060</t>
-  </si>
-  <si>
-    <t>0.9444,0.0165,0.0180,0.0060</t>
-  </si>
-  <si>
-    <t>0.0879,0.7619,0.6023,0.0023</t>
-  </si>
-  <si>
-    <t>0.2718,0.2293,0.6308,0.0020</t>
-  </si>
-  <si>
-    <t>0.4427,0.1971,0.4723,0.0059</t>
-  </si>
-  <si>
-    <t>0.3655,0.4122,0.3085,0.0019</t>
-  </si>
-  <si>
-    <t>0.2071,0.5591,0.4596,0.0018</t>
-  </si>
-  <si>
-    <t>0.2024,0.6062,0.3722,0.0008</t>
-  </si>
-  <si>
-    <t>0.8868,0.1129,0.0131,0.0035</t>
-  </si>
-  <si>
-    <t>0.8453,0.0612,0.0222,0.0280</t>
-  </si>
-  <si>
-    <t>0.9030,0.0836,0.0117,0.0033</t>
-  </si>
-  <si>
-    <t>0.9155,0.0392,0.0063,0.0054</t>
-  </si>
-  <si>
-    <t>0.8704,0.0883,0.0152,0.0084</t>
-  </si>
-  <si>
-    <t>0.8022,0.1207,0.0180,0.0147</t>
-  </si>
-  <si>
-    <t>0.7830,0.0693,0.0224,0.0439</t>
-  </si>
-  <si>
-    <t>0.6588,0.3305,0.0226,0.0062</t>
-  </si>
-  <si>
-    <t>0.7970,0.0539,0.0063,0.0325</t>
-  </si>
-  <si>
-    <t>0.8618,0.0738,0.0066,0.0118</t>
-  </si>
-  <si>
-    <t>0.9306,0.0337,0.0079,0.0123</t>
-  </si>
-  <si>
-    <t>0.9200,0.0538,0.0051,0.0042</t>
-  </si>
-  <si>
-    <t>0.8690,0.0752,0.0115,0.0137</t>
-  </si>
-  <si>
-    <t>0.6185,0.2760,0.0641,0.0362</t>
-  </si>
-  <si>
-    <t>0.8315,0.1602,0.0101,0.0035</t>
-  </si>
-  <si>
-    <t>0.6733,0.1086,0.0290,0.0874</t>
-  </si>
-  <si>
-    <t>0.6366,0.1044,0.3100,0.0040</t>
-  </si>
-  <si>
-    <t>0.8740,0.0144,0.1678,0.0006</t>
-  </si>
-  <si>
-    <t>0.9752,0.0029,0.0137,0.0032</t>
-  </si>
-  <si>
-    <t>0.9706,0.0062,0.0217,0.0004</t>
-  </si>
-  <si>
-    <t>0.1585,0.8619,0.0152,0.0040</t>
-  </si>
-  <si>
-    <t>0.4086,0.6484,0.0176,0.0039</t>
-  </si>
-  <si>
-    <t>0.6559,0.5456,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.8853,0.1473,0.0067,0.0005</t>
-  </si>
-  <si>
-    <t>0.6743,0.3485,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.0196,0.9842,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.8827,0.1642,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.9688,0.0167,0.0079,0.0006</t>
-  </si>
-  <si>
-    <t>0.9508,0.0187,0.0269,0.0007</t>
-  </si>
-  <si>
-    <t>0.9677,0.0052,0.0207,0.0007</t>
-  </si>
-  <si>
-    <t>0.9476,0.0224,0.0135,0.0010</t>
-  </si>
-  <si>
-    <t>0.9730,0.0060,0.0081,0.0028</t>
-  </si>
-  <si>
-    <t>0.7732,0.3241,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.0635,0.9450,0.0119,0.0013</t>
-  </si>
-  <si>
-    <t>0.8548,0.1728,0.0127,0.0006</t>
-  </si>
-  <si>
-    <t>0.5068,0.5823,0.0318,0.0006</t>
-  </si>
-  <si>
-    <t>0.9410,0.0782,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.4239,0.6298,0.0471,0.0039</t>
-  </si>
-  <si>
-    <t>0.6854,0.2964,0.0147,0.0089</t>
-  </si>
-  <si>
-    <t>0.9794,0.0181,0.0037,0.0007</t>
-  </si>
-  <si>
-    <t>0.9439,0.0270,0.0129,0.0047</t>
-  </si>
-  <si>
-    <t>0.6910,0.1284,0.0225,0.0531</t>
-  </si>
-  <si>
-    <t>0.9361,0.0239,0.0080,0.0096</t>
-  </si>
-  <si>
-    <t>0.9478,0.0341,0.0136,0.0034</t>
-  </si>
-  <si>
-    <t>0.9302,0.0485,0.0153,0.0034</t>
-  </si>
-  <si>
-    <t>0.8419,0.1426,0.0222,0.0073</t>
-  </si>
-  <si>
-    <t>0.8416,0.1002,0.0302,0.0220</t>
-  </si>
-  <si>
-    <t>0.7680,0.0896,0.1388,0.0012</t>
-  </si>
-  <si>
-    <t>0.5925,0.1993,0.2613,0.0026</t>
-  </si>
-  <si>
-    <t>0.3699,0.2835,0.3986,0.0021</t>
-  </si>
-  <si>
-    <t>0.9450,0.0098,0.0635,0.0007</t>
-  </si>
-  <si>
-    <t>0.9892,0.0014,0.0079,0.0002</t>
-  </si>
-  <si>
-    <t>0.9660,0.0060,0.0250,0.0012</t>
-  </si>
-  <si>
-    <t>0.9883,0.0036,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.9148,0.0509,0.0126,0.0028</t>
-  </si>
-  <si>
-    <t>0.9862,0.0046,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.9330,0.0076,0.0391,0.0125</t>
-  </si>
-  <si>
-    <t>0.9709,0.0049,0.0113,0.0036</t>
-  </si>
-  <si>
-    <t>0.8874,0.0151,0.0602,0.0201</t>
-  </si>
-  <si>
-    <t>0.1217,0.6804,0.5219,0.0037</t>
-  </si>
-  <si>
-    <t>0.9176,0.0684,0.0060,0.0014</t>
-  </si>
-  <si>
-    <t>0.7506,0.2678,0.0245,0.0046</t>
-  </si>
-  <si>
-    <t>0.8810,0.0392,0.0181,0.0241</t>
-  </si>
-  <si>
-    <t>0.4821,0.3857,0.0228,0.0101</t>
-  </si>
-  <si>
-    <t>0.9837,0.0073,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.8049,0.0582,0.0206,0.0311</t>
-  </si>
-  <si>
-    <t>0.9291,0.0478,0.0107,0.0024</t>
-  </si>
-  <si>
-    <t>0.2509,0.2953,0.6643,0.0640</t>
-  </si>
-  <si>
-    <t>0.9434,0.0135,0.0085,0.0064</t>
-  </si>
-  <si>
-    <t>0.9571,0.0153,0.0060,0.0036</t>
-  </si>
-  <si>
-    <t>0.9730,0.0157,0.0054,0.0004</t>
-  </si>
-  <si>
-    <t>0.9805,0.0059,0.0049,0.0009</t>
-  </si>
-  <si>
-    <t>0.9736,0.0120,0.0065,0.0014</t>
-  </si>
-  <si>
-    <t>0.9356,0.0390,0.0106,0.0010</t>
-  </si>
-  <si>
-    <t>0.9446,0.0469,0.0078,0.0014</t>
-  </si>
-  <si>
-    <t>0.9733,0.0124,0.0082,0.0009</t>
-  </si>
-  <si>
-    <t>0.9262,0.0448,0.0101,0.0049</t>
-  </si>
-  <si>
-    <t>0.8320,0.0582,0.0101,0.0214</t>
-  </si>
-  <si>
-    <t>0.8343,0.1354,0.0174,0.0063</t>
-  </si>
-  <si>
-    <t>0.8064,0.0992,0.0103,0.0143</t>
-  </si>
-  <si>
-    <t>0.9459,0.0266,0.0149,0.0047</t>
-  </si>
-  <si>
-    <t>0.8108,0.1546,0.0156,0.0081</t>
-  </si>
-  <si>
-    <t>0.6823,0.2591,0.0066,0.0063</t>
-  </si>
-  <si>
-    <t>0.8298,0.1323,0.0180,0.0116</t>
-  </si>
-  <si>
-    <t>0.8806,0.1473,0.0049,0.0006</t>
-  </si>
-  <si>
-    <t>0.7717,0.2595,0.0182,0.0048</t>
-  </si>
-  <si>
-    <t>0.7725,0.1952,0.0161,0.0065</t>
-  </si>
-  <si>
-    <t>0.9487,0.0248,0.0043,0.0026</t>
-  </si>
-  <si>
-    <t>0.8650,0.1083,0.0154,0.0048</t>
-  </si>
-  <si>
-    <t>0.9470,0.0229,0.0113,0.0054</t>
-  </si>
-  <si>
-    <t>0.9699,0.0178,0.0050,0.0013</t>
-  </si>
-  <si>
-    <t>0.7750,0.2185,0.0212,0.0048</t>
-  </si>
-  <si>
-    <t>0.0473,0.4484,0.7882,0.0043</t>
-  </si>
-  <si>
-    <t>0.9062,0.0641,0.0153,0.0095</t>
-  </si>
-  <si>
-    <t>0.8423,0.0344,0.1383,0.0017</t>
-  </si>
-  <si>
-    <t>0.9726,0.0023,0.0516,0.0003</t>
-  </si>
-  <si>
-    <t>0.9264,0.0118,0.0874,0.0008</t>
-  </si>
-  <si>
-    <t>0.5088,0.0367,0.6885,0.0009</t>
-  </si>
-  <si>
-    <t>0.6886,0.0767,0.2106,0.0015</t>
-  </si>
-  <si>
-    <t>0.5352,0.0671,0.4433,0.0017</t>
-  </si>
-  <si>
-    <t>0.8891,0.0237,0.1363,0.0013</t>
-  </si>
-  <si>
-    <t>0.9763,0.0088,0.0067,0.0002</t>
-  </si>
-  <si>
-    <t>0.9138,0.0373,0.0329,0.0017</t>
-  </si>
-  <si>
-    <t>0.9575,0.0209,0.0086,0.0011</t>
-  </si>
-  <si>
-    <t>0.8579,0.0341,0.1229,0.0021</t>
-  </si>
-  <si>
-    <t>0.9792,0.0073,0.0073,0.0005</t>
-  </si>
-  <si>
-    <t>0.9633,0.0343,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9444,0.0296,0.0144,0.0011</t>
-  </si>
-  <si>
-    <t>0.9720,0.0080,0.0189,0.0002</t>
-  </si>
-  <si>
-    <t>0.9177,0.0706,0.0122,0.0027</t>
-  </si>
-  <si>
-    <t>0.7891,0.2720,0.0035,0.0011</t>
-  </si>
-  <si>
-    <t>0.8440,0.0933,0.0371,0.0178</t>
-  </si>
-  <si>
-    <t>0.7007,0.2379,0.0156,0.0146</t>
-  </si>
-  <si>
-    <t>0.6791,0.2660,0.0102,0.0097</t>
-  </si>
-  <si>
-    <t>0.9780,0.0045,0.0076,0.0011</t>
-  </si>
-  <si>
-    <t>0.9925,0.0014,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9797,0.0025,0.0176,0.0011</t>
-  </si>
-  <si>
-    <t>0.9849,0.0024,0.0136,0.0003</t>
-  </si>
-  <si>
-    <t>0.9042,0.0311,0.0684,0.0039</t>
-  </si>
-  <si>
-    <t>0.7319,0.0330,0.2590,0.0013</t>
-  </si>
-  <si>
-    <t>0.6842,0.1653,0.1437,0.0013</t>
-  </si>
-  <si>
-    <t>0.8471,0.0309,0.1827,0.0044</t>
-  </si>
-  <si>
-    <t>0.9686,0.0035,0.0462,0.0007</t>
-  </si>
-  <si>
-    <t>0.4795,0.1136,0.4617,0.0027</t>
-  </si>
-  <si>
-    <t>0.8901,0.0477,0.0067,0.0080</t>
-  </si>
-  <si>
-    <t>0.9109,0.1018,0.0037,0.0008</t>
-  </si>
-  <si>
-    <t>0.9021,0.0857,0.0076,0.0019</t>
-  </si>
-  <si>
-    <t>0.8805,0.0990,0.0173,0.0037</t>
-  </si>
-  <si>
-    <t>0.5929,0.2577,0.0184,0.0193</t>
-  </si>
-  <si>
-    <t>0.8819,0.0596,0.0098,0.0107</t>
-  </si>
-  <si>
-    <t>0.8013,0.0785,0.0161,0.0310</t>
-  </si>
-  <si>
-    <t>0.7675,0.1119,0.0093,0.0185</t>
-  </si>
-  <si>
-    <t>0.9376,0.0479,0.0130,0.0013</t>
-  </si>
-  <si>
-    <t>0.9837,0.0133,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9694,0.0131,0.0141,0.0012</t>
-  </si>
-  <si>
-    <t>0.9356,0.0173,0.0676,0.0009</t>
-  </si>
-  <si>
-    <t>0.7089,0.0434,0.3702,0.0037</t>
-  </si>
-  <si>
-    <t>0.8920,0.0237,0.1118,0.0011</t>
-  </si>
-  <si>
-    <t>0.4408,0.0208,0.7132,0.0003</t>
-  </si>
-  <si>
-    <t>0.9387,0.0214,0.0450,0.0022</t>
-  </si>
-  <si>
-    <t>0.4208,0.3381,0.3508,0.0416</t>
-  </si>
-  <si>
-    <t>0.5101,0.1962,0.3571,0.0143</t>
-  </si>
-  <si>
-    <t>0.9578,0.0112,0.0240,0.0004</t>
-  </si>
-  <si>
-    <t>0.9802,0.0011,0.0258,0.0007</t>
-  </si>
-  <si>
-    <t>0.9879,0.0020,0.0065,0.0005</t>
-  </si>
-  <si>
-    <t>0.9784,0.0046,0.0119,0.0011</t>
-  </si>
-  <si>
-    <t>0.9467,0.0359,0.0086,0.0028</t>
-  </si>
-  <si>
-    <t>0.8565,0.0908,0.0116,0.0075</t>
-  </si>
-  <si>
-    <t>0.9263,0.0439,0.0058,0.0055</t>
-  </si>
-  <si>
-    <t>0.7933,0.1423,0.0070,0.0069</t>
-  </si>
-  <si>
-    <t>0.7954,0.1732,0.0199,0.0066</t>
-  </si>
-  <si>
-    <t>0.9275,0.0532,0.0109,0.0033</t>
-  </si>
-  <si>
-    <t>0.4098,0.5652,0.0224,0.0130</t>
-  </si>
-  <si>
-    <t>0.7607,0.1026,0.0218,0.0274</t>
-  </si>
-  <si>
-    <t>0.9661,0.0098,0.0282,0.0003</t>
-  </si>
-  <si>
-    <t>0.8115,0.0899,0.0659,0.0003</t>
-  </si>
-  <si>
-    <t>0.6882,0.1087,0.2026,0.0017</t>
-  </si>
-  <si>
-    <t>0.9241,0.0276,0.0538,0.0008</t>
-  </si>
-  <si>
-    <t>0.7030,0.0369,0.4046,0.0012</t>
-  </si>
-  <si>
-    <t>0.9705,0.0052,0.0303,0.0008</t>
-  </si>
-  <si>
-    <t>0.8708,0.0288,0.1160,0.0013</t>
-  </si>
-  <si>
-    <t>0.9355,0.0172,0.0775,0.0030</t>
-  </si>
-  <si>
-    <t>0.9566,0.0076,0.0093,0.0060</t>
-  </si>
-  <si>
-    <t>0.9613,0.0074,0.0250,0.0043</t>
-  </si>
-  <si>
-    <t>0.9399,0.0086,0.0426,0.0090</t>
-  </si>
-  <si>
-    <t>0.9573,0.0078,0.0134,0.0056</t>
-  </si>
-  <si>
-    <t>0.9766,0.0012,0.0093,0.0048</t>
-  </si>
-  <si>
-    <t>0.9758,0.0069,0.0051,0.0011</t>
+    <t>0.6767,0.0438,0.0056,0.2898</t>
+  </si>
+  <si>
+    <t>0.0087,0.0057,0.0071,0.9902</t>
+  </si>
+  <si>
+    <t>0.8037,0.0056,0.0094,0.2073</t>
+  </si>
+  <si>
+    <t>0.0239,0.0024,0.0029,0.9855</t>
+  </si>
+  <si>
+    <t>0.9965,0.0003,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9950,0.0005,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.9953,0.0004,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9957,0.0004,0.0002,0.0026</t>
+  </si>
+  <si>
+    <t>0.9734,0.0021,0.0007,0.0196</t>
+  </si>
+  <si>
+    <t>0.9893,0.0033,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.9916,0.0010,0.0003,0.0049</t>
+  </si>
+  <si>
+    <t>0.9908,0.0006,0.0004,0.0070</t>
+  </si>
+  <si>
+    <t>0.9621,0.0048,0.0340,0.0021</t>
+  </si>
+  <si>
+    <t>0.5935,0.0032,0.6591,0.0004</t>
+  </si>
+  <si>
+    <t>0.0918,0.0070,0.9271,0.0005</t>
+  </si>
+  <si>
+    <t>0.6570,0.0142,0.3826,0.0020</t>
+  </si>
+  <si>
+    <t>0.8661,0.0035,0.2071,0.0029</t>
+  </si>
+  <si>
+    <t>0.0070,0.9874,0.0074,0.0018</t>
+  </si>
+  <si>
+    <t>0.0192,0.9729,0.0050,0.0080</t>
+  </si>
+  <si>
+    <t>0.0929,0.9183,0.0070,0.0026</t>
+  </si>
+  <si>
+    <t>0.0175,0.9816,0.0036,0.0030</t>
+  </si>
+  <si>
+    <t>0.0016,0.9964,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9291,0.0022,0.0873,0.0060</t>
+  </si>
+  <si>
+    <t>0.1952,0.0033,0.8510,0.0072</t>
+  </si>
+  <si>
+    <t>0.0020,0.0057,0.9853,0.0166</t>
+  </si>
+  <si>
+    <t>0.0744,0.0195,0.9036,0.0116</t>
+  </si>
+  <si>
+    <t>0.0026,0.0051,0.9878,0.0085</t>
+  </si>
+  <si>
+    <t>0.0736,0.0513,0.8764,0.0353</t>
+  </si>
+  <si>
+    <t>0.0033,0.0008,0.9906,0.0062</t>
+  </si>
+  <si>
+    <t>0.1951,0.8415,0.0124,0.0055</t>
+  </si>
+  <si>
+    <t>0.8128,0.0471,0.1583,0.0312</t>
+  </si>
+  <si>
+    <t>0.0004,0.0024,0.9959,0.0085</t>
+  </si>
+  <si>
+    <t>0.0516,0.3865,0.4894,0.0056</t>
+  </si>
+  <si>
+    <t>0.8732,0.0723,0.0423,0.0303</t>
+  </si>
+  <si>
+    <t>0.9610,0.0170,0.0162,0.0029</t>
+  </si>
+  <si>
+    <t>0.5585,0.6018,0.0083,0.0010</t>
+  </si>
+  <si>
+    <t>0.0088,0.9774,0.1455,0.0013</t>
+  </si>
+  <si>
+    <t>0.0108,0.8944,0.0296,0.0540</t>
+  </si>
+  <si>
+    <t>0.0298,0.0009,0.9582,0.0084</t>
+  </si>
+  <si>
+    <t>0.0189,0.0064,0.9685,0.0056</t>
+  </si>
+  <si>
+    <t>0.0606,0.0055,0.5060,0.4924</t>
+  </si>
+  <si>
+    <t>0.0174,0.0120,0.9793,0.0015</t>
+  </si>
+  <si>
+    <t>0.0019,0.9831,0.0089,0.0035</t>
+  </si>
+  <si>
+    <t>0.0019,0.0032,0.9911,0.0025</t>
+  </si>
+  <si>
+    <t>0.0364,0.3674,0.0095,0.8243</t>
+  </si>
+  <si>
+    <t>0.0057,0.9781,0.0311,0.0390</t>
+  </si>
+  <si>
+    <t>0.0036,0.9697,0.0517,0.0084</t>
+  </si>
+  <si>
+    <t>0.0063,0.9825,0.0130,0.0043</t>
+  </si>
+  <si>
+    <t>0.0050,0.0018,0.9917,0.0025</t>
+  </si>
+  <si>
+    <t>0.0011,0.0394,0.9912,0.0053</t>
+  </si>
+  <si>
+    <t>0.0027,0.0036,0.9883,0.0041</t>
+  </si>
+  <si>
+    <t>0.0103,0.0091,0.9733,0.0123</t>
+  </si>
+  <si>
+    <t>0.0017,0.2354,0.9908,0.0011</t>
+  </si>
+  <si>
+    <t>0.0046,0.0431,0.9850,0.0015</t>
+  </si>
+  <si>
+    <t>0.9585,0.0686,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9723,0.0059,0.0070,0.0091</t>
+  </si>
+  <si>
+    <t>0.9426,0.0261,0.0190,0.0161</t>
+  </si>
+  <si>
+    <t>0.0010,0.0067,0.9927,0.0079</t>
+  </si>
+  <si>
+    <t>0.9857,0.0040,0.0113,0.0019</t>
+  </si>
+  <si>
+    <t>0.9867,0.0055,0.0026,0.0040</t>
+  </si>
+  <si>
+    <t>0.9770,0.0248,0.0055,0.0009</t>
+  </si>
+  <si>
+    <t>0.0038,0.7405,0.9669,0.0006</t>
+  </si>
+  <si>
+    <t>0.0027,0.0426,0.9932,0.0025</t>
+  </si>
+  <si>
+    <t>0.0097,0.0280,0.9563,0.0133</t>
+  </si>
+  <si>
+    <t>0.0049,0.4662,0.9619,0.0009</t>
+  </si>
+  <si>
+    <t>0.0087,0.0039,0.9889,0.0011</t>
+  </si>
+  <si>
+    <t>0.1007,0.8732,0.0590,0.0072</t>
+  </si>
+  <si>
+    <t>0.0212,0.9822,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9583,0.0171,0.0366,0.0030</t>
+  </si>
+  <si>
+    <t>0.7649,0.1297,0.1696,0.0230</t>
+  </si>
+  <si>
+    <t>0.0048,0.2328,0.9755,0.0016</t>
+  </si>
+  <si>
+    <t>0.0028,0.5990,0.9483,0.0006</t>
+  </si>
+  <si>
+    <t>0.0059,0.6595,0.8742,0.0017</t>
+  </si>
+  <si>
+    <t>0.0017,0.9878,0.1324,0.0019</t>
+  </si>
+  <si>
+    <t>0.0006,0.9702,0.9360,0.0001</t>
+  </si>
+  <si>
+    <t>0.0038,0.0001,0.0088,0.9931</t>
+  </si>
+  <si>
+    <t>0.0015,0.0006,0.0003,0.9989</t>
+  </si>
+  <si>
+    <t>0.0018,0.0012,0.0025,0.9979</t>
+  </si>
+  <si>
+    <t>0.0231,0.0018,0.0097,0.9831</t>
+  </si>
+  <si>
+    <t>0.0041,0.0030,0.0048,0.9950</t>
+  </si>
+  <si>
+    <t>0.0010,0.0371,0.0018,0.9955</t>
+  </si>
+  <si>
+    <t>0.0001,0.9402,0.9785,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.8451,0.9378,0.0025</t>
+  </si>
+  <si>
+    <t>0.0584,0.2853,0.8052,0.0413</t>
+  </si>
+  <si>
+    <t>0.0025,0.7886,0.9002,0.0010</t>
+  </si>
+  <si>
+    <t>0.0011,0.8943,0.9120,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.9623,0.4047,0.0006</t>
+  </si>
+  <si>
+    <t>0.9953,0.0004,0.0005,0.0028</t>
+  </si>
+  <si>
+    <t>0.9926,0.0056,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9866,0.0095,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9965,0.0006,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9832,0.0099,0.0018,0.0039</t>
+  </si>
+  <si>
+    <t>0.9955,0.0005,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9877,0.0037,0.0009,0.0052</t>
+  </si>
+  <si>
+    <t>0.9940,0.0022,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9922,0.0018,0.0006,0.0031</t>
+  </si>
+  <si>
+    <t>0.9921,0.0005,0.0003,0.0069</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9875,0.0037,0.0016,0.0046</t>
+  </si>
+  <si>
+    <t>0.9882,0.0054,0.0027,0.0025</t>
+  </si>
+  <si>
+    <t>0.9886,0.0013,0.0006,0.0085</t>
+  </si>
+  <si>
+    <t>0.9951,0.0005,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.0029,0.0034,0.9914,0.0047</t>
+  </si>
+  <si>
+    <t>0.0537,0.4209,0.7508,0.0627</t>
+  </si>
+  <si>
+    <t>0.5637,0.0802,0.3139,0.1045</t>
+  </si>
+  <si>
+    <t>0.0011,0.0011,0.9908,0.0106</t>
+  </si>
+  <si>
+    <t>0.2404,0.8396,0.0027,0.0024</t>
+  </si>
+  <si>
+    <t>0.0152,0.9856,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.0375,0.9657,0.0009,0.0074</t>
+  </si>
+  <si>
+    <t>0.0770,0.9227,0.0073,0.0107</t>
+  </si>
+  <si>
+    <t>0.0760,0.9427,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.0124,0.9872,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.8567,0.2490,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.6325,0.0089,0.5380,0.0027</t>
+  </si>
+  <si>
+    <t>0.2919,0.0101,0.7813,0.0097</t>
+  </si>
+  <si>
+    <t>0.3803,0.2728,0.2851,0.0892</t>
+  </si>
+  <si>
+    <t>0.7637,0.0322,0.2059,0.0470</t>
+  </si>
+  <si>
+    <t>0.4299,0.1506,0.3853,0.2137</t>
+  </si>
+  <si>
+    <t>0.0033,0.9908,0.0096,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.9918,0.0031,0.0187</t>
+  </si>
+  <si>
+    <t>0.0012,0.9939,0.0069,0.0286</t>
+  </si>
+  <si>
+    <t>0.0004,0.9192,0.9603,0.0002</t>
+  </si>
+  <si>
+    <t>0.0056,0.9929,0.0139,0.0002</t>
+  </si>
+  <si>
+    <t>0.1560,0.8453,0.0626,0.0042</t>
+  </si>
+  <si>
+    <t>0.7252,0.3274,0.0133,0.0010</t>
+  </si>
+  <si>
+    <t>0.9862,0.0061,0.0081,0.0019</t>
+  </si>
+  <si>
+    <t>0.9810,0.0054,0.0033,0.0081</t>
+  </si>
+  <si>
+    <t>0.9908,0.0006,0.0009,0.0049</t>
+  </si>
+  <si>
+    <t>0.9142,0.0353,0.0495,0.0241</t>
+  </si>
+  <si>
+    <t>0.9936,0.0008,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.9935,0.0017,0.0057,0.0005</t>
+  </si>
+  <si>
+    <t>0.9823,0.0024,0.0010,0.0120</t>
+  </si>
+  <si>
+    <t>0.9793,0.0040,0.0069,0.0069</t>
+  </si>
+  <si>
+    <t>0.0066,0.5743,0.9360,0.0024</t>
+  </si>
+  <si>
+    <t>0.0002,0.5925,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0136,0.0349,0.9658,0.0009</t>
+  </si>
+  <si>
+    <t>0.0620,0.1465,0.9144,0.0030</t>
+  </si>
+  <si>
+    <t>0.9455,0.0210,0.0161,0.0072</t>
+  </si>
+  <si>
+    <t>0.7645,0.0474,0.0695,0.0704</t>
+  </si>
+  <si>
+    <t>0.6102,0.0023,0.5738,0.0044</t>
+  </si>
+  <si>
+    <t>0.5127,0.3421,0.1096,0.0995</t>
+  </si>
+  <si>
+    <t>0.0060,0.0013,0.0041,0.9945</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.0009,0.9996</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.0005,0.9993</t>
+  </si>
+  <si>
+    <t>0.0016,0.0002,0.0008,0.9988</t>
+  </si>
+  <si>
+    <t>0.0012,0.9106,0.5412,0.0047</t>
+  </si>
+  <si>
+    <t>0.9835,0.0031,0.0016,0.0076</t>
+  </si>
+  <si>
+    <t>0.1848,0.8564,0.0039,0.0177</t>
+  </si>
+  <si>
+    <t>0.9927,0.0025,0.0017,0.0015</t>
+  </si>
+  <si>
+    <t>0.9466,0.0628,0.0077,0.0015</t>
+  </si>
+  <si>
+    <t>0.9676,0.0038,0.0024,0.0218</t>
+  </si>
+  <si>
+    <t>0.0743,0.0063,0.0023,0.9497</t>
+  </si>
+  <si>
+    <t>0.9748,0.0045,0.0023,0.0145</t>
+  </si>
+  <si>
+    <t>0.0032,0.0037,0.9709,0.0562</t>
+  </si>
+  <si>
+    <t>0.8010,0.0005,0.0019,0.3080</t>
+  </si>
+  <si>
+    <t>0.6800,0.0113,0.0075,0.3432</t>
+  </si>
+  <si>
+    <t>0.6505,0.3113,0.0683,0.0070</t>
+  </si>
+  <si>
+    <t>0.8576,0.0364,0.0027,0.0457</t>
+  </si>
+  <si>
+    <t>0.9901,0.0018,0.0080,0.0005</t>
+  </si>
+  <si>
+    <t>0.6047,0.2754,0.1043,0.0336</t>
+  </si>
+  <si>
+    <t>0.9387,0.0194,0.0621,0.0050</t>
+  </si>
+  <si>
+    <t>0.9598,0.0269,0.0078,0.0031</t>
+  </si>
+  <si>
+    <t>0.9823,0.0041,0.0019,0.0070</t>
+  </si>
+  <si>
+    <t>0.9778,0.0033,0.0012,0.0133</t>
+  </si>
+  <si>
+    <t>0.9917,0.0017,0.0014,0.0028</t>
+  </si>
+  <si>
+    <t>0.9753,0.0002,0.0002,0.0323</t>
+  </si>
+  <si>
+    <t>0.9959,0.0009,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9819,0.0038,0.0035,0.0061</t>
+  </si>
+  <si>
+    <t>0.9698,0.0007,0.0002,0.0290</t>
+  </si>
+  <si>
+    <t>0.9852,0.0006,0.0006,0.0135</t>
+  </si>
+  <si>
+    <t>0.7451,0.3687,0.0034,0.0045</t>
+  </si>
+  <si>
+    <t>0.2921,0.7442,0.0257,0.0038</t>
+  </si>
+  <si>
+    <t>0.5636,0.5483,0.0039,0.0035</t>
+  </si>
+  <si>
+    <t>0.9645,0.0110,0.0073,0.0134</t>
+  </si>
+  <si>
+    <t>0.9915,0.0031,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.9674,0.0168,0.0010,0.0074</t>
+  </si>
+  <si>
+    <t>0.9886,0.0039,0.0023,0.0032</t>
+  </si>
+  <si>
+    <t>0.9634,0.0247,0.0028,0.0078</t>
+  </si>
+  <si>
+    <t>0.0004,0.0141,0.9958,0.0031</t>
+  </si>
+  <si>
+    <t>0.9443,0.0444,0.0132,0.0031</t>
+  </si>
+  <si>
+    <t>0.0009,0.0022,0.9966,0.0008</t>
+  </si>
+  <si>
+    <t>0.0116,0.4209,0.8470,0.0077</t>
+  </si>
+  <si>
+    <t>0.0507,0.0050,0.9540,0.0047</t>
+  </si>
+  <si>
+    <t>0.0128,0.0401,0.9832,0.0030</t>
+  </si>
+  <si>
+    <t>0.0007,0.0053,0.9940,0.0024</t>
+  </si>
+  <si>
+    <t>0.0021,0.0065,0.9925,0.0024</t>
+  </si>
+  <si>
+    <t>0.0010,0.0077,0.9937,0.0045</t>
+  </si>
+  <si>
+    <t>0.2137,0.0510,0.7505,0.0189</t>
+  </si>
+  <si>
+    <t>0.1831,0.0092,0.8416,0.0166</t>
+  </si>
+  <si>
+    <t>0.6632,0.1546,0.2536,0.0238</t>
+  </si>
+  <si>
+    <t>0.0556,0.1654,0.7793,0.0049</t>
+  </si>
+  <si>
+    <t>0.1241,0.0332,0.8687,0.0028</t>
+  </si>
+  <si>
+    <t>0.2891,0.3139,0.2667,0.0128</t>
+  </si>
+  <si>
+    <t>0.5869,0.0281,0.5044,0.0253</t>
+  </si>
+  <si>
+    <t>0.0612,0.0478,0.8737,0.0249</t>
+  </si>
+  <si>
+    <t>0.6505,0.4901,0.0058,0.0027</t>
+  </si>
+  <si>
+    <t>0.8047,0.3137,0.0025,0.0026</t>
+  </si>
+  <si>
+    <t>0.9842,0.0100,0.0047,0.0015</t>
+  </si>
+  <si>
+    <t>0.9848,0.0105,0.0043,0.0027</t>
+  </si>
+  <si>
+    <t>0.9377,0.0762,0.0088,0.0073</t>
+  </si>
+  <si>
+    <t>0.8090,0.0698,0.0925,0.0344</t>
+  </si>
+  <si>
+    <t>0.7109,0.0055,0.3631,0.0115</t>
+  </si>
+  <si>
+    <t>0.8280,0.0245,0.0690,0.0723</t>
+  </si>
+  <si>
+    <t>0.5643,0.0034,0.5615,0.0099</t>
+  </si>
+  <si>
+    <t>0.5945,0.0117,0.3497,0.0750</t>
+  </si>
+  <si>
+    <t>0.0080,0.0139,0.9752,0.0070</t>
+  </si>
+  <si>
+    <t>0.0098,0.4515,0.8568,0.0052</t>
+  </si>
+  <si>
+    <t>0.0192,0.3694,0.9170,0.0420</t>
+  </si>
+  <si>
+    <t>0.0252,0.0215,0.9392,0.0235</t>
+  </si>
+  <si>
+    <t>0.0009,0.0665,0.7188,0.0597</t>
+  </si>
+  <si>
+    <t>0.9749,0.0053,0.0024,0.0160</t>
+  </si>
+  <si>
+    <t>0.9804,0.0056,0.0018,0.0086</t>
+  </si>
+  <si>
+    <t>0.9906,0.0022,0.0009,0.0034</t>
+  </si>
+  <si>
+    <t>0.9818,0.0194,0.0017,0.0014</t>
+  </si>
+  <si>
+    <t>0.9768,0.0125,0.0016,0.0043</t>
+  </si>
+  <si>
+    <t>0.9924,0.0014,0.0024,0.0023</t>
+  </si>
+  <si>
+    <t>0.9816,0.0173,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.9957,0.0005,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.0156,0.0562,0.9601,0.0170</t>
+  </si>
+  <si>
+    <t>0.1332,0.3922,0.5753,0.0873</t>
+  </si>
+  <si>
+    <t>0.9646,0.0115,0.0221,0.0032</t>
+  </si>
+  <si>
+    <t>0.0006,0.0016,0.9977,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.0029,0.9932,0.0119</t>
+  </si>
+  <si>
+    <t>0.0037,0.1018,0.9810,0.0026</t>
+  </si>
+  <si>
+    <t>0.0084,0.0016,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.1192,0.0248,0.8903,0.0058</t>
+  </si>
+  <si>
+    <t>0.0017,0.0028,0.9977,0.0005</t>
+  </si>
+  <si>
+    <t>0.0275,0.3507,0.6519,0.0378</t>
+  </si>
+  <si>
+    <t>0.4000,0.0922,0.5199,0.0085</t>
+  </si>
+  <si>
+    <t>0.9477,0.0041,0.0446,0.0042</t>
+  </si>
+  <si>
+    <t>0.7991,0.0007,0.3235,0.0028</t>
+  </si>
+  <si>
+    <t>0.6580,0.0126,0.0560,0.3136</t>
+  </si>
+  <si>
+    <t>0.9880,0.0038,0.0015,0.0041</t>
+  </si>
+  <si>
+    <t>0.9899,0.0077,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9867,0.0035,0.0023,0.0052</t>
+  </si>
+  <si>
+    <t>0.9949,0.0027,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9826,0.0021,0.0011,0.0138</t>
+  </si>
+  <si>
+    <t>0.9772,0.0134,0.0032,0.0054</t>
+  </si>
+  <si>
+    <t>0.9945,0.0010,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.9901,0.0038,0.0010,0.0029</t>
+  </si>
+  <si>
+    <t>0.0011,0.0060,0.9930,0.0016</t>
+  </si>
+  <si>
+    <t>0.0076,0.0359,0.9817,0.0021</t>
+  </si>
+  <si>
+    <t>0.0029,0.0276,0.9806,0.0070</t>
+  </si>
+  <si>
+    <t>0.0596,0.0090,0.9398,0.0060</t>
+  </si>
+  <si>
+    <t>0.0064,0.0037,0.9900,0.0022</t>
+  </si>
+  <si>
+    <t>0.0569,0.0533,0.4546,0.6364</t>
+  </si>
+  <si>
+    <t>0.3169,0.0714,0.6730,0.0227</t>
+  </si>
+  <si>
+    <t>0.0579,0.0854,0.8474,0.0242</t>
+  </si>
+  <si>
+    <t>0.6978,0.0005,0.0025,0.4048</t>
+  </si>
+  <si>
+    <t>0.0205,0.0065,0.0115,0.9816</t>
+  </si>
+  <si>
+    <t>0.4352,0.0021,0.0010,0.7823</t>
+  </si>
+  <si>
+    <t>0.0004,0.0014,0.0008,0.9993</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.7488,0.0069,0.0092,0.3250</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3549,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
         <v>378</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4809,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>468</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5131,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
         <v>491</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5299,7 +5299,7 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D241" t="s">
         <v>503</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
